--- a/data/trans_orig/P78_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P78_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona sustentadora principal trabaja actualmente en 2023</t>
+          <t>Población según si la persona sustentadora principal trabaja actualmente en 2023 (tasa de respuesta: 99,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>355153</t>
+          <t>351351</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>382381</t>
+          <t>382683</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>345236</t>
+          <t>347400</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>375975</t>
+          <t>376708</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>713037</t>
+          <t>713601</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>753797</t>
+          <t>754132</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,14%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11529</t>
+          <t>11227</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38757</t>
+          <t>42559</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>115833</t>
+          <t>115100</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>146572</t>
+          <t>144408</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>131921</t>
+          <t>131586</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>172681</t>
+          <t>172117</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,43%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>862224</t>
+          <t>863781</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>909477</t>
+          <t>911082</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>563299</t>
+          <t>563277</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>601717</t>
+          <t>602004</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1421397</t>
+          <t>1420439</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1544539</t>
+          <t>1563794</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14507</t>
+          <t>12902</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61760</t>
+          <t>60203</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>160959</t>
+          <t>160672</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>199377</t>
+          <t>199399</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>142121</t>
+          <t>122866</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>265263</t>
+          <t>266221</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>404473</t>
+          <t>402661</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>434605</t>
+          <t>433748</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>199389</t>
+          <t>206726</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>622220</t>
+          <t>625859</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>522138</t>
+          <t>536482</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1060431</t>
+          <t>1059404</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,34%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19158</t>
+          <t>20015</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49290</t>
+          <t>51102</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>151062</t>
+          <t>147423</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>573893</t>
+          <t>566556</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>166614</t>
+          <t>167641</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>704907</t>
+          <t>690563</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>56,28%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>535823</t>
+          <t>535624</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>573933</t>
+          <t>574278</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>617035</t>
+          <t>615079</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>694919</t>
+          <t>692845</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1173685</t>
+          <t>1173995</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1242511</t>
+          <t>1243756</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,24%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24300</t>
+          <t>23955</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62410</t>
+          <t>62609</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>149062</t>
+          <t>151136</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>226946</t>
+          <t>228902</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>199703</t>
+          <t>198458</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>268529</t>
+          <t>268219</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2201831</t>
+          <t>2200055</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2279414</t>
+          <t>2279383</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1435238</t>
+          <t>1615442</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2215378</t>
+          <t>2223083</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3739116</t>
+          <t>3712386</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4491567</t>
+          <t>4486477</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,59%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90475</t>
+          <t>90506</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>168058</t>
+          <t>169834</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>656370</t>
+          <t>648665</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1436510</t>
+          <t>1256306</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>750070</t>
+          <t>755160</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1502521</t>
+          <t>1529251</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P78_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P78_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>374127</t>
+          <t>408569</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>351351</t>
+          <t>394333</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>382683</t>
+          <t>416279</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>362041</t>
+          <t>396081</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>347400</t>
+          <t>378744</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>376708</t>
+          <t>411961</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>736168</t>
+          <t>804650</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>713601</t>
+          <t>783642</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>754132</t>
+          <t>823183</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,53%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19783</t>
+          <t>18767</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11227</t>
+          <t>11057</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42559</t>
+          <t>33003</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>129767</t>
+          <t>138987</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>115100</t>
+          <t>123107</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>144408</t>
+          <t>156324</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>149550</t>
+          <t>157753</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>131586</t>
+          <t>139220</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>172117</t>
+          <t>178761</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>18,57%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>393910</t>
+          <t>427336</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>393910</t>
+          <t>427336</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>393910</t>
+          <t>427336</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>491808</t>
+          <t>535068</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>491808</t>
+          <t>535068</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>491808</t>
+          <t>535068</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>885718</t>
+          <t>962403</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>885718</t>
+          <t>962403</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>885718</t>
+          <t>962403</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>886929</t>
+          <t>711762</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>863781</t>
+          <t>691926</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>911082</t>
+          <t>725527</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>583497</t>
+          <t>655418</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>563277</t>
+          <t>634696</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>602004</t>
+          <t>676525</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1470426</t>
+          <t>1367179</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1420439</t>
+          <t>1339134</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1563794</t>
+          <t>1393813</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>87,08%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>37055</t>
+          <t>38642</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12902</t>
+          <t>24877</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>60203</t>
+          <t>58478</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>179179</t>
+          <t>194751</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>160672</t>
+          <t>173644</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>199399</t>
+          <t>215473</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>216234</t>
+          <t>233393</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>122866</t>
+          <t>206759</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>266221</t>
+          <t>261438</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>923984</t>
+          <t>750404</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>923984</t>
+          <t>750404</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>923984</t>
+          <t>750404</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>762676</t>
+          <t>850169</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>762676</t>
+          <t>850169</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>762676</t>
+          <t>850169</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1686660</t>
+          <t>1600572</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1686660</t>
+          <t>1600572</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1686660</t>
+          <t>1600572</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>422005</t>
+          <t>486177</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>402661</t>
+          <t>468527</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>433748</t>
+          <t>498634</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>451110</t>
+          <t>497538</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>206726</t>
+          <t>477558</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>625859</t>
+          <t>513758</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>873115</t>
+          <t>983715</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>536482</t>
+          <t>956791</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1059404</t>
+          <t>1006298</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>88,11%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31758</t>
+          <t>32434</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20015</t>
+          <t>19977</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51102</t>
+          <t>50084</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>322172</t>
+          <t>125964</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147423</t>
+          <t>109744</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>566556</t>
+          <t>145944</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>353930</t>
+          <t>158398</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>167641</t>
+          <t>135815</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>690563</t>
+          <t>185322</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>453763</t>
+          <t>518611</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>453763</t>
+          <t>518611</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>453763</t>
+          <t>518611</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>773282</t>
+          <t>623502</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>773282</t>
+          <t>623502</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>773282</t>
+          <t>623502</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1227045</t>
+          <t>1142113</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1227045</t>
+          <t>1142113</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1227045</t>
+          <t>1142113</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>558795</t>
+          <t>611364</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>535624</t>
+          <t>592358</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>574278</t>
+          <t>624861</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>646785</t>
+          <t>637428</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>615079</t>
+          <t>612786</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>692845</t>
+          <t>658453</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1205580</t>
+          <t>1248793</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1173995</t>
+          <t>1220204</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1243756</t>
+          <t>1277805</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>85,71%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>39438</t>
+          <t>36677</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23955</t>
+          <t>23180</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62609</t>
+          <t>55683</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>197196</t>
+          <t>205338</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>151136</t>
+          <t>184313</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>228902</t>
+          <t>229980</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>236634</t>
+          <t>242015</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>198458</t>
+          <t>213003</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>268219</t>
+          <t>270604</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,15%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>598233</t>
+          <t>648041</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>598233</t>
+          <t>648041</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>598233</t>
+          <t>648041</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>843981</t>
+          <t>842766</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>843981</t>
+          <t>842766</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>843981</t>
+          <t>842766</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1442214</t>
+          <t>1490808</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1442214</t>
+          <t>1490808</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1442214</t>
+          <t>1490808</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2241856</t>
+          <t>2217872</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2200055</t>
+          <t>2183529</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2279383</t>
+          <t>2244972</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2043434</t>
+          <t>2186466</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1615442</t>
+          <t>2146726</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2223083</t>
+          <t>2227347</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4285290</t>
+          <t>4404338</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3712386</t>
+          <t>4351225</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4486477</t>
+          <t>4453396</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,71%</t>
         </is>
       </c>
     </row>
@@ -2210,17 +2210,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>128033</t>
+          <t>126520</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90506</t>
+          <t>99420</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>169834</t>
+          <t>160863</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>828314</t>
+          <t>665039</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>648665</t>
+          <t>624158</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1256306</t>
+          <t>704779</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>956347</t>
+          <t>791559</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>755160</t>
+          <t>742501</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1529251</t>
+          <t>844672</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2369889</t>
+          <t>2344392</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2369889</t>
+          <t>2344392</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2369889</t>
+          <t>2344392</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2871748</t>
+          <t>2851505</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2871748</t>
+          <t>2851505</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2871748</t>
+          <t>2851505</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>5241637</t>
+          <t>5195897</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5241637</t>
+          <t>5195897</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5241637</t>
+          <t>5195897</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
